--- a/AAII_Financials/Quarterly/BREA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BREA_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="92">
   <si>
     <t>BREA</t>
   </si>
@@ -656,44 +656,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44742</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44377</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="H7" s="2" t="s">
         <v>3</v>
       </c>
@@ -709,23 +710,26 @@
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>100</v>
+      </c>
+      <c r="E8" s="3">
         <v>200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>200</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
       </c>
@@ -741,22 +745,25 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
         <v>100</v>
       </c>
-      <c r="E9" s="3">
-        <v>0</v>
-      </c>
       <c r="F9" s="3">
         <v>0</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
+      <c r="G9" s="3">
+        <v>0</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -773,8 +780,11 @@
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -785,11 +795,11 @@
         <v>100</v>
       </c>
       <c r="F10" s="3">
+        <v>100</v>
+      </c>
+      <c r="G10" s="3">
         <v>200</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
       </c>
@@ -805,8 +815,11 @@
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -819,8 +832,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -851,8 +865,11 @@
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -883,8 +900,11 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -915,8 +935,11 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -929,8 +952,8 @@
       <c r="F15" s="3">
         <v>0</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>3</v>
+      <c r="G15" s="3">
+        <v>0</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>3</v>
@@ -947,8 +970,11 @@
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -958,22 +984,23 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E17" s="3">
         <v>1500</v>
-      </c>
-      <c r="E17" s="3">
-        <v>200</v>
       </c>
       <c r="F17" s="3">
         <v>200</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>3</v>
+      <c r="G17" s="3">
+        <v>200</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>3</v>
@@ -990,23 +1017,26 @@
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>100</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1022,8 +1052,11 @@
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1036,8 +1069,9 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1048,11 +1082,11 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1068,22 +1102,25 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1200</v>
       </c>
-      <c r="E21" s="3">
-        <v>0</v>
-      </c>
       <c r="F21" s="3">
         <v>0</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
+      <c r="G21" s="3">
+        <v>0</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
@@ -1100,8 +1137,11 @@
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1114,8 +1154,8 @@
       <c r="F22" s="3">
         <v>0</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
+      <c r="G22" s="3">
+        <v>0</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
@@ -1126,28 +1166,31 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-100</v>
       </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>3</v>
+      <c r="G23" s="3">
+        <v>0</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>3</v>
@@ -1164,8 +1207,11 @@
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1178,8 +1224,8 @@
       <c r="F24" s="3">
         <v>0</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
+      <c r="G24" s="3">
+        <v>0</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -1196,8 +1242,11 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1228,22 +1277,25 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-100</v>
       </c>
-      <c r="F26" s="3">
-        <v>0</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>3</v>
+      <c r="G26" s="3">
+        <v>0</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>3</v>
@@ -1260,22 +1312,25 @@
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-100</v>
       </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>3</v>
+      <c r="G27" s="3">
+        <v>0</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>3</v>
@@ -1292,8 +1347,11 @@
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1324,8 +1382,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1356,8 +1417,11 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1388,8 +1452,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1420,8 +1487,11 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1432,11 +1502,11 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1452,22 +1522,25 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-100</v>
       </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>3</v>
+      <c r="G33" s="3">
+        <v>0</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>3</v>
@@ -1484,8 +1557,11 @@
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1516,22 +1592,25 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-100</v>
       </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>3</v>
+      <c r="G35" s="3">
+        <v>0</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>3</v>
@@ -1548,28 +1627,31 @@
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44742</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44377</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="H38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1585,8 +1667,11 @@
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1599,8 +1684,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1613,19 +1699,20 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E41" s="3">
         <v>400</v>
       </c>
-      <c r="E41" s="3">
-        <v>0</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>3</v>
+      <c r="F41" s="3">
+        <v>0</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>3</v>
@@ -1645,8 +1732,11 @@
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1677,20 +1767,23 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3">
         <v>100</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1709,8 +1802,11 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1741,20 +1837,23 @@
       <c r="L44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>100</v>
+      </c>
+      <c r="E45" s="3">
         <v>500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>100</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1773,20 +1872,23 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E46" s="3">
         <v>900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>200</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1805,31 +1907,34 @@
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -1837,20 +1942,23 @@
       <c r="L47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3">
         <v>300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>400</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1869,31 +1977,34 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
-      </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
+        <v>900</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -1901,8 +2012,11 @@
       <c r="L49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1933,8 +2047,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1965,8 +2082,11 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -1997,8 +2117,11 @@
       <c r="L52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2029,20 +2152,23 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>600</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2061,8 +2187,11 @@
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2075,8 +2204,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2089,20 +2219,21 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>400</v>
+      </c>
+      <c r="E57" s="3">
         <v>700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>500</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2121,19 +2252,22 @@
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E58" s="3">
         <v>100</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
+      <c r="F58" s="3">
+        <v>100</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>3</v>
@@ -2153,8 +2287,11 @@
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2162,11 +2299,11 @@
         <v>300</v>
       </c>
       <c r="E59" s="3">
+        <v>300</v>
+      </c>
+      <c r="F59" s="3">
         <v>100</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2185,20 +2322,23 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>900</v>
+      </c>
+      <c r="E60" s="3">
         <v>1100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>700</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2217,19 +2357,22 @@
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
         <v>300</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -2249,40 +2392,46 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
+        <v>400</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
+        <v>0</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2313,8 +2462,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2345,8 +2497,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2377,8 +2532,11 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -2386,11 +2544,11 @@
         <v>1400</v>
       </c>
       <c r="E66" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F66" s="3">
         <v>1000</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2409,8 +2567,11 @@
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2423,8 +2584,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2455,8 +2617,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2487,8 +2652,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2519,8 +2687,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2551,20 +2722,23 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-400</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2583,8 +2757,11 @@
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2615,8 +2792,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2647,8 +2827,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2679,20 +2862,23 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E76" s="3">
         <v>-100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-400</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2711,8 +2897,11 @@
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2743,28 +2932,31 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44742</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44377</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="H80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2780,22 +2972,25 @@
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-100</v>
       </c>
-      <c r="F81" s="3">
-        <v>0</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>3</v>
+      <c r="G81" s="3">
+        <v>0</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>3</v>
@@ -2812,8 +3007,11 @@
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2826,22 +3024,23 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
         <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="G83" s="3">
+        <v>0</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
@@ -2858,8 +3057,11 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2890,8 +3092,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2922,8 +3127,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2954,8 +3162,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2986,8 +3197,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3018,22 +3232,25 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1000</v>
       </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
       <c r="F89" s="3">
         <v>0</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
+      <c r="G89" s="3">
+        <v>0</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
@@ -3050,8 +3267,11 @@
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3064,13 +3284,14 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -3090,14 +3311,17 @@
       <c r="J91" s="3">
         <v>0</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
+      <c r="K91" s="3">
+        <v>0</v>
       </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3128,8 +3352,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3160,13 +3387,16 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
@@ -3174,8 +3404,8 @@
       <c r="F94" s="3">
         <v>0</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
+      <c r="G94" s="3">
+        <v>0</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
@@ -3192,8 +3422,11 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3206,8 +3439,9 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3238,8 +3472,11 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3270,8 +3507,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3302,8 +3542,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3334,22 +3577,25 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E100" s="3">
         <v>1300</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
+      <c r="G100" s="3">
+        <v>0</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
@@ -3366,16 +3612,19 @@
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
         <v>0</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
+      <c r="E101" s="3">
+        <v>0</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>3</v>
@@ -3392,28 +3641,31 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E102" s="3">
         <v>300</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
         <v>0</v>
       </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
+      <c r="G102" s="3">
+        <v>0</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>3</v>
@@ -3428,6 +3680,9 @@
         <v>3</v>
       </c>
       <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BREA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BREA_QTR_FIN.xlsx
@@ -1181,7 +1181,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-1700</v>
+        <v>-1600</v>
       </c>
       <c r="E23" s="3">
         <v>-1300</v>
@@ -1286,7 +1286,7 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-1700</v>
+        <v>-1600</v>
       </c>
       <c r="E26" s="3">
         <v>-1300</v>
@@ -1321,7 +1321,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-1700</v>
+        <v>-1600</v>
       </c>
       <c r="E27" s="3">
         <v>-1300</v>
@@ -1531,7 +1531,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-1700</v>
+        <v>-1600</v>
       </c>
       <c r="E33" s="3">
         <v>-1300</v>
@@ -1601,7 +1601,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-1700</v>
+        <v>-1600</v>
       </c>
       <c r="E35" s="3">
         <v>-1300</v>
@@ -2541,7 +2541,7 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="E66" s="3">
         <v>1400</v>
@@ -2731,7 +2731,7 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4900</v>
+        <v>4800</v>
       </c>
       <c r="E72" s="3">
         <v>-200</v>
@@ -2981,7 +2981,7 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-1700</v>
+        <v>-1600</v>
       </c>
       <c r="E81" s="3">
         <v>-1300</v>

--- a/AAII_Financials/Quarterly/BREA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BREA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="92">
   <si>
     <t>BREA</t>
   </si>
@@ -656,48 +656,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44377</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I7" s="2" t="s">
         <v>3</v>
       </c>
@@ -713,26 +714,29 @@
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E8" s="3">
         <v>100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>200</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
       </c>
@@ -748,25 +752,28 @@
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
         <v>100</v>
       </c>
-      <c r="F9" s="3">
-        <v>0</v>
-      </c>
       <c r="G9" s="3">
         <v>0</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
+      <c r="H9" s="3">
+        <v>0</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
@@ -783,13 +790,16 @@
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="E10" s="3">
         <v>100</v>
@@ -798,11 +808,11 @@
         <v>100</v>
       </c>
       <c r="G10" s="3">
+        <v>100</v>
+      </c>
+      <c r="H10" s="3">
         <v>200</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
       </c>
@@ -818,8 +828,11 @@
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -833,8 +846,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -868,8 +882,11 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -903,31 +920,34 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
         <v>0</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -938,8 +958,11 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -955,8 +978,8 @@
       <c r="G15" s="3">
         <v>0</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
+      <c r="H15" s="3">
+        <v>0</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>3</v>
@@ -973,8 +996,11 @@
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -985,25 +1011,26 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E17" s="3">
         <v>1800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1500</v>
-      </c>
-      <c r="F17" s="3">
-        <v>200</v>
       </c>
       <c r="G17" s="3">
         <v>200</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
+      <c r="H17" s="3">
+        <v>200</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>3</v>
@@ -1020,26 +1047,29 @@
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>100</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1055,8 +1085,11 @@
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1070,13 +1103,14 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1085,11 +1119,11 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1105,25 +1139,28 @@
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1200</v>
       </c>
-      <c r="F21" s="3">
-        <v>0</v>
-      </c>
       <c r="G21" s="3">
         <v>0</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
+      <c r="H21" s="3">
+        <v>0</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
@@ -1140,8 +1177,11 @@
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1157,8 +1197,8 @@
       <c r="G22" s="3">
         <v>0</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
+      <c r="H22" s="3">
+        <v>0</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
@@ -1169,31 +1209,34 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-1600</v>
+        <v>-5400</v>
       </c>
       <c r="E23" s="3">
-        <v>-1300</v>
+        <v>-1700</v>
       </c>
       <c r="F23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="G23" s="3">
         <v>-100</v>
       </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
+      <c r="H23" s="3">
+        <v>0</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>3</v>
@@ -1210,8 +1253,11 @@
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1227,8 +1273,8 @@
       <c r="G24" s="3">
         <v>0</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
+      <c r="H24" s="3">
+        <v>0</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
@@ -1245,8 +1291,11 @@
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1280,25 +1329,28 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-1600</v>
+        <v>-5400</v>
       </c>
       <c r="E26" s="3">
-        <v>-1300</v>
+        <v>-1700</v>
       </c>
       <c r="F26" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="G26" s="3">
         <v>-100</v>
       </c>
-      <c r="G26" s="3">
-        <v>0</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
+      <c r="H26" s="3">
+        <v>0</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>3</v>
@@ -1315,25 +1367,28 @@
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-1600</v>
+        <v>-4900</v>
       </c>
       <c r="E27" s="3">
-        <v>-1300</v>
+        <v>-1700</v>
       </c>
       <c r="F27" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="G27" s="3">
         <v>-100</v>
       </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
+      <c r="H27" s="3">
+        <v>0</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>3</v>
@@ -1350,8 +1405,11 @@
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1385,8 +1443,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1420,8 +1481,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1455,8 +1519,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1490,13 +1557,16 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -1505,11 +1575,11 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1525,25 +1595,28 @@
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-1600</v>
+        <v>-4900</v>
       </c>
       <c r="E33" s="3">
-        <v>-1300</v>
+        <v>-1700</v>
       </c>
       <c r="F33" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="G33" s="3">
         <v>-100</v>
       </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
+      <c r="H33" s="3">
+        <v>0</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>3</v>
@@ -1560,8 +1633,11 @@
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1595,25 +1671,28 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-1600</v>
+        <v>-4900</v>
       </c>
       <c r="E35" s="3">
-        <v>-1300</v>
+        <v>-1700</v>
       </c>
       <c r="F35" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="G35" s="3">
         <v>-100</v>
       </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
+      <c r="H35" s="3">
+        <v>0</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>3</v>
@@ -1630,31 +1709,34 @@
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44377</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1670,8 +1752,11 @@
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1685,8 +1770,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1700,22 +1786,23 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="E41" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F41" s="3">
         <v>400</v>
       </c>
-      <c r="F41" s="3">
-        <v>0</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
+      <c r="G41" s="3">
+        <v>0</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
@@ -1735,8 +1822,11 @@
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1770,23 +1860,26 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>600</v>
+      </c>
+      <c r="E43" s="3">
         <v>100</v>
       </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
       <c r="F43" s="3">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3">
         <v>100</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1805,8 +1898,11 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1840,8 +1936,11 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1849,14 +1948,14 @@
         <v>100</v>
       </c>
       <c r="E45" s="3">
+        <v>100</v>
+      </c>
+      <c r="F45" s="3">
         <v>500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1875,22 +1974,25 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5200</v>
+        <v>3300</v>
       </c>
       <c r="E46" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F46" s="3">
         <v>900</v>
       </c>
-      <c r="F46" s="3">
-        <v>200</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
+      <c r="G46" s="3">
+        <v>300</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
@@ -1910,17 +2012,20 @@
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>500</v>
+      </c>
+      <c r="E47" s="3">
         <v>100</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1936,8 +2041,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -1945,23 +2050,26 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E48" s="3">
+        <v>0</v>
+      </c>
+      <c r="F48" s="3">
         <v>300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>400</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1980,16 +2088,19 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>900</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>3</v>
+        <v>4500</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1000</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>3</v>
@@ -2006,8 +2117,8 @@
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
+      <c r="K49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
@@ -2015,8 +2126,11 @@
       <c r="M49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2050,8 +2164,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2085,8 +2202,11 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2120,8 +2240,11 @@
       <c r="M52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2155,22 +2278,25 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6300</v>
+        <v>9400</v>
       </c>
       <c r="E54" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F54" s="3">
         <v>1200</v>
       </c>
-      <c r="F54" s="3">
-        <v>600</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
+      <c r="G54" s="3">
+        <v>700</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
@@ -2190,8 +2316,11 @@
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2205,8 +2334,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2220,23 +2350,24 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E57" s="3">
         <v>400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>500</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2255,22 +2386,25 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>300</v>
+      </c>
+      <c r="E58" s="3">
         <v>200</v>
-      </c>
-      <c r="E58" s="3">
-        <v>100</v>
       </c>
       <c r="F58" s="3">
         <v>100</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
+      <c r="G58" s="3">
+        <v>100</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
@@ -2290,23 +2424,26 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="E59" s="3">
         <v>300</v>
       </c>
       <c r="F59" s="3">
+        <v>300</v>
+      </c>
+      <c r="G59" s="3">
         <v>100</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2325,23 +2462,26 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E60" s="3">
         <v>900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>700</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2360,22 +2500,25 @@
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="E61" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
         <v>300</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2395,17 +2538,20 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>200</v>
+      </c>
+      <c r="E62" s="3">
         <v>400</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2421,17 +2567,20 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
+        <v>0</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2465,8 +2614,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2500,8 +2652,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2535,23 +2690,26 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1300</v>
+        <v>6600</v>
       </c>
       <c r="E66" s="3">
         <v>1400</v>
       </c>
       <c r="F66" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G66" s="3">
         <v>1000</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2570,8 +2728,11 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2585,8 +2746,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2620,8 +2782,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2655,8 +2820,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2690,8 +2858,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2725,23 +2896,26 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4800</v>
+        <v>2600</v>
       </c>
       <c r="E72" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-400</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2760,8 +2934,11 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2795,8 +2972,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2830,8 +3010,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2865,23 +3048,26 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4900</v>
+        <v>2800</v>
       </c>
       <c r="E76" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F76" s="3">
         <v>-100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-400</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2900,8 +3086,11 @@
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2935,31 +3124,34 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44377</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2975,25 +3167,28 @@
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-1600</v>
+        <v>-4900</v>
       </c>
       <c r="E81" s="3">
-        <v>-1300</v>
+        <v>-1700</v>
       </c>
       <c r="F81" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="G81" s="3">
         <v>-100</v>
       </c>
-      <c r="G81" s="3">
-        <v>0</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
+      <c r="H81" s="3">
+        <v>0</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>3</v>
@@ -3010,8 +3205,11 @@
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3025,25 +3223,26 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
         <v>100</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
@@ -3060,8 +3259,11 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3095,8 +3297,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3130,8 +3335,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3165,8 +3373,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3200,8 +3411,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3235,25 +3449,28 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1000</v>
       </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
       <c r="G89" s="3">
         <v>0</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
+      <c r="H89" s="3">
+        <v>0</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>3</v>
@@ -3270,8 +3487,11 @@
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3285,8 +3505,9 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3294,7 +3515,7 @@
         <v>-100</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -3314,14 +3535,17 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
+      <c r="L91" s="3">
+        <v>0</v>
       </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3355,8 +3579,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3390,25 +3617,28 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1000</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
+      <c r="H94" s="3">
+        <v>0</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
@@ -3425,8 +3655,11 @@
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3440,8 +3673,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3475,8 +3709,11 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3510,8 +3747,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3545,8 +3785,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3580,25 +3823,28 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>6400</v>
+        <v>7000</v>
       </c>
       <c r="E100" s="3">
-        <v>1300</v>
+        <v>6500</v>
       </c>
       <c r="F100" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
+      <c r="H100" s="3">
+        <v>0</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
@@ -3615,8 +3861,11 @@
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3626,8 +3875,8 @@
       <c r="E101" s="3">
         <v>0</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
+      <c r="F101" s="3">
+        <v>0</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>3</v>
@@ -3644,31 +3893,34 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>4600</v>
+        <v>2200</v>
       </c>
       <c r="E102" s="3">
-        <v>300</v>
+        <v>4700</v>
       </c>
       <c r="F102" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G102" s="3">
         <v>0</v>
       </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
+      <c r="H102" s="3">
+        <v>0</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>3</v>
@@ -3683,6 +3935,9 @@
         <v>3</v>
       </c>
       <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BREA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BREA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
   <si>
     <t>BREA</t>
   </si>
@@ -662,11 +662,12 @@
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -688,22 +689,22 @@
         <v>45291</v>
       </c>
       <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
+        <v>44834</v>
+      </c>
+      <c r="J7" s="2">
         <v>44742</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44377</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
@@ -723,25 +724,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="E8" s="3">
+        <v>600</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
         <v>100</v>
-      </c>
-      <c r="F8" s="3">
-        <v>200</v>
-      </c>
-      <c r="G8" s="3">
-        <v>100</v>
-      </c>
-      <c r="H8" s="3">
-        <v>200</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -764,10 +765,10 @@
         <v>100</v>
       </c>
       <c r="E9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
@@ -775,11 +776,11 @@
       <c r="H9" s="3">
         <v>0</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -799,25 +800,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="E10" s="3">
+        <v>500</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
         <v>100</v>
-      </c>
-      <c r="F10" s="3">
-        <v>100</v>
-      </c>
-      <c r="G10" s="3">
-        <v>100</v>
-      </c>
-      <c r="H10" s="3">
-        <v>200</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -931,14 +932,14 @@
       <c r="D14" s="3">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -981,11 +982,11 @@
       <c r="H15" s="3">
         <v>0</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
@@ -1018,25 +1019,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>7200</v>
+        <v>2800</v>
       </c>
       <c r="E17" s="3">
-        <v>1800</v>
+        <v>2700</v>
       </c>
       <c r="F17" s="3">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="G17" s="3">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="H17" s="3">
-        <v>200</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
+        <v>600</v>
+      </c>
+      <c r="I17" s="3">
+        <v>600</v>
+      </c>
+      <c r="J17" s="3">
+        <v>100</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -1056,25 +1057,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-6000</v>
+        <v>-2200</v>
       </c>
       <c r="E18" s="3">
-        <v>-1700</v>
+        <v>-2100</v>
       </c>
       <c r="F18" s="3">
-        <v>-1300</v>
+        <v>-700</v>
       </c>
       <c r="G18" s="3">
-        <v>-100</v>
+        <v>-700</v>
       </c>
       <c r="H18" s="3">
-        <v>100</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+        <v>-600</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1110,25 +1111,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>600</v>
+        <v>-400</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1148,25 +1149,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-5000</v>
+        <v>-1800</v>
       </c>
       <c r="E21" s="3">
-        <v>-1600</v>
+        <v>-1800</v>
       </c>
       <c r="F21" s="3">
-        <v>-1200</v>
+        <v>-800</v>
       </c>
       <c r="G21" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="H21" s="3">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>-600</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1200,11 +1201,11 @@
       <c r="H22" s="3">
         <v>0</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1224,25 +1225,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-5400</v>
+        <v>-1900</v>
       </c>
       <c r="E23" s="3">
-        <v>-1700</v>
+        <v>-1800</v>
       </c>
       <c r="F23" s="3">
-        <v>-1400</v>
+        <v>-800</v>
       </c>
       <c r="G23" s="3">
-        <v>-100</v>
+        <v>-800</v>
       </c>
       <c r="H23" s="3">
-        <v>0</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
+        <v>-600</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1276,11 +1277,11 @@
       <c r="H24" s="3">
         <v>0</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1338,25 +1339,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-5400</v>
+        <v>-1900</v>
       </c>
       <c r="E26" s="3">
-        <v>-1700</v>
+        <v>-1800</v>
       </c>
       <c r="F26" s="3">
-        <v>-1400</v>
+        <v>-800</v>
       </c>
       <c r="G26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J26" s="3">
         <v>-100</v>
-      </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1376,25 +1377,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-4900</v>
+        <v>-1600</v>
       </c>
       <c r="E27" s="3">
-        <v>-1700</v>
+        <v>-1500</v>
       </c>
       <c r="F27" s="3">
-        <v>-1400</v>
+        <v>-800</v>
       </c>
       <c r="G27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J27" s="3">
         <v>-100</v>
-      </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1566,25 +1567,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-600</v>
+        <v>400</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>100</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1604,25 +1605,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-4900</v>
+        <v>-1600</v>
       </c>
       <c r="E33" s="3">
-        <v>-1700</v>
+        <v>-1500</v>
       </c>
       <c r="F33" s="3">
-        <v>-1400</v>
+        <v>-800</v>
       </c>
       <c r="G33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J33" s="3">
         <v>-100</v>
-      </c>
-      <c r="H33" s="3">
-        <v>0</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1680,25 +1681,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-4900</v>
+        <v>-1600</v>
       </c>
       <c r="E35" s="3">
-        <v>-1700</v>
+        <v>-1500</v>
       </c>
       <c r="F35" s="3">
-        <v>-1400</v>
+        <v>-800</v>
       </c>
       <c r="G35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J35" s="3">
         <v>-100</v>
-      </c>
-      <c r="H35" s="3">
-        <v>0</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1726,22 +1727,22 @@
         <v>45291</v>
       </c>
       <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
+        <v>44834</v>
+      </c>
+      <c r="J38" s="2">
         <v>44742</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44377</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
@@ -1796,22 +1797,22 @@
         <v>2500</v>
       </c>
       <c r="E41" s="3">
-        <v>5100</v>
+        <v>2400</v>
       </c>
       <c r="F41" s="3">
+        <v>5000</v>
+      </c>
+      <c r="G41" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H41" s="3">
         <v>400</v>
       </c>
-      <c r="G41" s="3">
-        <v>0</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+      <c r="I41" s="3">
+        <v>300</v>
+      </c>
+      <c r="J41" s="3">
+        <v>0</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1872,22 +1873,22 @@
         <v>600</v>
       </c>
       <c r="E43" s="3">
+        <v>600</v>
+      </c>
+      <c r="F43" s="3">
         <v>100</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
       </c>
       <c r="G43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+      <c r="H43" s="3">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3">
+        <v>100</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1906,26 +1907,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -1944,23 +1945,23 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>100</v>
-      </c>
-      <c r="E45" s="3">
-        <v>100</v>
-      </c>
-      <c r="F45" s="3">
-        <v>500</v>
-      </c>
-      <c r="G45" s="3">
-        <v>100</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
+        <v>300</v>
+      </c>
+      <c r="I45" s="3">
+        <v>300</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
@@ -1986,22 +1987,22 @@
         <v>3300</v>
       </c>
       <c r="E46" s="3">
-        <v>5300</v>
+        <v>3100</v>
       </c>
       <c r="F46" s="3">
+        <v>5200</v>
+      </c>
+      <c r="G46" s="3">
+        <v>5200</v>
+      </c>
+      <c r="H46" s="3">
         <v>900</v>
       </c>
-      <c r="G46" s="3">
-        <v>300</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+      <c r="I46" s="3">
+        <v>800</v>
+      </c>
+      <c r="J46" s="3">
+        <v>200</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -2024,13 +2025,13 @@
         <v>500</v>
       </c>
       <c r="E47" s="3">
+        <v>500</v>
+      </c>
+      <c r="F47" s="3">
         <v>100</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
+      <c r="G47" s="3">
+        <v>100</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
@@ -2062,22 +2063,22 @@
         <v>1200</v>
       </c>
       <c r="E48" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="F48" s="3">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3">
+        <v>0</v>
+      </c>
+      <c r="H48" s="3">
         <v>300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
+        <v>300</v>
+      </c>
+      <c r="J48" s="3">
         <v>400</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -2100,22 +2101,22 @@
         <v>4500</v>
       </c>
       <c r="E49" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+        <v>4300</v>
+      </c>
+      <c r="F49" s="3">
+        <v>900</v>
+      </c>
+      <c r="G49" s="3">
+        <v>900</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2210,26 +2211,26 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2290,22 +2291,22 @@
         <v>9400</v>
       </c>
       <c r="E54" s="3">
-        <v>6400</v>
+        <v>9000</v>
       </c>
       <c r="F54" s="3">
+        <v>6300</v>
+      </c>
+      <c r="G54" s="3">
+        <v>6300</v>
+      </c>
+      <c r="H54" s="3">
         <v>1200</v>
       </c>
-      <c r="G54" s="3">
-        <v>700</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+      <c r="I54" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J54" s="3">
+        <v>600</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2357,25 +2358,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4100</v>
+        <v>3900</v>
       </c>
       <c r="E57" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F57" s="3">
         <v>400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
+        <v>400</v>
+      </c>
+      <c r="H57" s="3">
         <v>700</v>
       </c>
-      <c r="G57" s="3">
-        <v>500</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+      <c r="I57" s="3">
+        <v>600</v>
+      </c>
+      <c r="J57" s="3">
+        <v>100</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2398,22 +2399,22 @@
         <v>300</v>
       </c>
       <c r="E58" s="3">
+        <v>300</v>
+      </c>
+      <c r="F58" s="3">
         <v>200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
+        <v>200</v>
+      </c>
+      <c r="H58" s="3">
         <v>100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>100</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+      <c r="J58" s="3">
+        <v>100</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2436,22 +2437,22 @@
         <v>600</v>
       </c>
       <c r="E59" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="F59" s="3">
         <v>300</v>
       </c>
       <c r="G59" s="3">
-        <v>100</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+        <v>300</v>
+      </c>
+      <c r="H59" s="3">
+        <v>300</v>
+      </c>
+      <c r="I59" s="3">
+        <v>300</v>
+      </c>
+      <c r="J59" s="3">
+        <v>500</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2474,22 +2475,22 @@
         <v>5000</v>
       </c>
       <c r="E60" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F60" s="3">
         <v>900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
+        <v>900</v>
+      </c>
+      <c r="H60" s="3">
         <v>1100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J60" s="3">
         <v>700</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2512,22 +2513,22 @@
         <v>900</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
+        <v>200</v>
+      </c>
+      <c r="J61" s="3">
         <v>300</v>
-      </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3">
-        <v>0</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2550,13 +2551,13 @@
         <v>200</v>
       </c>
       <c r="E62" s="3">
+        <v>200</v>
+      </c>
+      <c r="F62" s="3">
         <v>400</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
+      <c r="G62" s="3">
+        <v>400</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -2699,25 +2700,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>6600</v>
+        <v>6100</v>
       </c>
       <c r="E66" s="3">
-        <v>1400</v>
+        <v>5900</v>
       </c>
       <c r="F66" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="G66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I66" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J66" s="3">
         <v>1000</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2905,25 +2906,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2600</v>
+        <v>-6600</v>
       </c>
       <c r="E72" s="3">
-        <v>5000</v>
+        <v>-6300</v>
       </c>
       <c r="F72" s="3">
-        <v>-200</v>
+        <v>-3300</v>
       </c>
       <c r="G72" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="H72" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="J72" s="3">
         <v>-400</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -3060,22 +3061,22 @@
         <v>2800</v>
       </c>
       <c r="E76" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F76" s="3">
         <v>5000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
+        <v>4900</v>
+      </c>
+      <c r="H76" s="3">
         <v>-100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J76" s="3">
         <v>-400</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -3141,22 +3142,22 @@
         <v>45291</v>
       </c>
       <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
+        <v>44834</v>
+      </c>
+      <c r="J80" s="2">
         <v>44742</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44377</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
@@ -3176,25 +3177,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-4900</v>
+        <v>-1600</v>
       </c>
       <c r="E81" s="3">
-        <v>-1700</v>
+        <v>-1500</v>
       </c>
       <c r="F81" s="3">
-        <v>-1400</v>
+        <v>-800</v>
       </c>
       <c r="G81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J81" s="3">
         <v>-100</v>
-      </c>
-      <c r="H81" s="3">
-        <v>0</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -3230,25 +3231,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
       </c>
       <c r="F83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H83" s="3">
         <v>0</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -3458,25 +3459,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-2700</v>
+        <v>-900</v>
       </c>
       <c r="E89" s="3">
-        <v>-800</v>
+        <v>-900</v>
       </c>
       <c r="F89" s="3">
-        <v>-1000</v>
+        <v>-400</v>
       </c>
       <c r="G89" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+        <v>-500</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J89" s="3">
+        <v>0</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -3517,11 +3518,11 @@
       <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -3626,25 +3627,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-2200</v>
+        <v>-600</v>
       </c>
       <c r="E94" s="3">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
       <c r="F94" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="G94" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3679,26 +3680,26 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3832,25 +3833,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>7000</v>
+        <v>300</v>
       </c>
       <c r="E100" s="3">
-        <v>6500</v>
+        <v>300</v>
       </c>
       <c r="F100" s="3">
-        <v>1400</v>
+        <v>3200</v>
       </c>
       <c r="G100" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+        <v>700</v>
+      </c>
+      <c r="I100" s="3">
+        <v>600</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3875,8 +3876,8 @@
       <c r="E101" s="3">
         <v>0</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>3</v>
@@ -3908,25 +3909,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>2200</v>
+        <v>-1300</v>
       </c>
       <c r="E102" s="3">
-        <v>4700</v>
+        <v>-1200</v>
       </c>
       <c r="F102" s="3">
-        <v>400</v>
+        <v>2300</v>
       </c>
       <c r="G102" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="I102" s="3">
+        <v>200</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Quarterly/BREA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BREA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="92">
   <si>
     <t>BREA</t>
   </si>
@@ -656,85 +656,93 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>900</v>
+      </c>
+      <c r="E8" s="3">
+        <v>900</v>
+      </c>
+      <c r="F8" s="3">
         <v>600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>600</v>
       </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
       <c r="H8" s="3">
         <v>0</v>
       </c>
@@ -742,22 +750,28 @@
         <v>0</v>
       </c>
       <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
         <v>100</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -768,10 +782,10 @@
         <v>100</v>
       </c>
       <c r="F9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9" s="3">
         <v>0</v>
@@ -782,11 +796,11 @@
       <c r="J9" s="3">
         <v>0</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
+      <c r="K9" s="3">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3">
+        <v>0</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
@@ -794,23 +808,29 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>800</v>
+      </c>
+      <c r="F10" s="3">
         <v>500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>500</v>
       </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3">
-        <v>0</v>
-      </c>
       <c r="H10" s="3">
         <v>0</v>
       </c>
@@ -818,22 +838,28 @@
         <v>0</v>
       </c>
       <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
         <v>100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -848,8 +874,10 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -886,8 +914,14 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -924,8 +958,14 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -941,20 +981,20 @@
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -962,16 +1002,22 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
@@ -988,11 +1034,11 @@
       <c r="J15" s="3">
         <v>0</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
@@ -1000,8 +1046,14 @@
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1013,75 +1065,83 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F17" s="3">
         <v>2800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2700</v>
       </c>
-      <c r="F17" s="3">
-        <v>800</v>
-      </c>
-      <c r="G17" s="3">
-        <v>800</v>
-      </c>
       <c r="H17" s="3">
+        <v>900</v>
+      </c>
+      <c r="I17" s="3">
+        <v>900</v>
+      </c>
+      <c r="J17" s="3">
         <v>600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>100</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-2100</v>
       </c>
-      <c r="F18" s="3">
-        <v>-700</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-700</v>
-      </c>
       <c r="H18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="J18" s="3">
         <v>-600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-600</v>
       </c>
-      <c r="J18" s="3">
-        <v>0</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
+      <c r="L18" s="3">
+        <v>0</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
@@ -1089,8 +1149,14 @@
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1105,23 +1171,25 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-400</v>
       </c>
-      <c r="F20" s="3">
-        <v>100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>100</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
@@ -1131,11 +1199,11 @@
       <c r="J20" s="3">
         <v>0</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
@@ -1143,37 +1211,43 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-1800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-600</v>
       </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
+      <c r="L21" s="3">
+        <v>0</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
@@ -1181,8 +1255,14 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1207,49 +1287,55 @@
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-600</v>
       </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
+      <c r="L23" s="3">
+        <v>0</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
@@ -1257,16 +1343,22 @@
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
@@ -1283,11 +1375,11 @@
       <c r="J24" s="3">
         <v>0</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
@@ -1295,8 +1387,14 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1333,46 +1431,58 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-100</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1380,37 +1490,43 @@
         <v>-1600</v>
       </c>
       <c r="E27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G27" s="3">
         <v>-1500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-100</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1447,8 +1563,14 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1485,8 +1607,14 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1523,8 +1651,14 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1561,23 +1695,29 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>400</v>
       </c>
-      <c r="F32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-100</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
@@ -1587,11 +1727,11 @@
       <c r="J32" s="3">
         <v>0</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
@@ -1599,8 +1739,14 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1608,37 +1754,43 @@
         <v>-1600</v>
       </c>
       <c r="E33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G33" s="3">
         <v>-1500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-100</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1675,8 +1827,14 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1684,80 +1842,92 @@
         <v>-1600</v>
       </c>
       <c r="E35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G35" s="3">
         <v>-1500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-100</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1772,8 +1942,10 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1788,37 +1960,39 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>500</v>
+      </c>
+      <c r="F41" s="3">
         <v>2500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>2400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>5000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>5000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>300</v>
       </c>
-      <c r="J41" s="3">
-        <v>0</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
+      <c r="L41" s="3">
+        <v>0</v>
       </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
@@ -1826,8 +2000,14 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1864,54 +2044,66 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>800</v>
+      </c>
+      <c r="F43" s="3">
         <v>600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
       <c r="J43" s="3">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
         <v>100</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>3</v>
+      <c r="D44" s="3">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>3</v>
@@ -1928,11 +2120,11 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -1940,8 +2132,14 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1957,18 +2155,18 @@
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>300</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1978,84 +2176,102 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F46" s="3">
         <v>3300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>3100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>5200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>5200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>200</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>100</v>
+      </c>
+      <c r="E47" s="3">
+        <v>100</v>
+      </c>
+      <c r="F47" s="3">
         <v>500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>100</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2063,75 +2279,87 @@
         <v>1200</v>
       </c>
       <c r="E48" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F48" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G48" s="3">
         <v>1100</v>
       </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
       <c r="H48" s="3">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3">
         <v>300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>400</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F49" s="3">
         <v>4500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>4300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>900</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="M49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2168,8 +2396,14 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2206,8 +2440,14 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2232,11 +2472,11 @@
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -2244,8 +2484,14 @@
       <c r="N52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2282,46 +2528,58 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>6800</v>
+      </c>
+      <c r="F54" s="3">
         <v>9400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>9000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>6300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>6300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>600</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2336,8 +2594,10 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2352,46 +2612,54 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F57" s="3">
         <v>3900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>3700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2402,25 +2670,25 @@
         <v>300</v>
       </c>
       <c r="F58" s="3">
+        <v>300</v>
+      </c>
+      <c r="G58" s="3">
+        <v>300</v>
+      </c>
+      <c r="H58" s="3">
         <v>200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>200</v>
-      </c>
-      <c r="H58" s="3">
-        <v>100</v>
-      </c>
-      <c r="I58" s="3">
-        <v>100</v>
       </c>
       <c r="J58" s="3">
         <v>100</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
+      <c r="K58" s="3">
+        <v>100</v>
+      </c>
+      <c r="L58" s="3">
+        <v>100</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
@@ -2428,22 +2696,28 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>300</v>
+      </c>
+      <c r="F59" s="3">
         <v>600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>600</v>
-      </c>
-      <c r="F59" s="3">
-        <v>300</v>
-      </c>
-      <c r="G59" s="3">
-        <v>300</v>
       </c>
       <c r="H59" s="3">
         <v>300</v>
@@ -2452,89 +2726,101 @@
         <v>300</v>
       </c>
       <c r="J59" s="3">
+        <v>300</v>
+      </c>
+      <c r="K59" s="3">
+        <v>300</v>
+      </c>
+      <c r="L59" s="3">
         <v>500</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F60" s="3">
         <v>5000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>4800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>700</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>800</v>
+      </c>
+      <c r="E61" s="3">
+        <v>800</v>
+      </c>
+      <c r="F61" s="3">
         <v>900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>900</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
         <v>300</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -2542,46 +2828,58 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F62" s="3">
         <v>200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>400</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2618,8 +2916,14 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2656,8 +2960,14 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2694,8 +3004,14 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -2703,37 +3019,43 @@
         <v>6100</v>
       </c>
       <c r="E66" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F66" s="3">
+        <v>6100</v>
+      </c>
+      <c r="G66" s="3">
         <v>5900</v>
-      </c>
-      <c r="F66" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G66" s="3">
-        <v>1300</v>
       </c>
       <c r="H66" s="3">
         <v>1300</v>
       </c>
       <c r="I66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K66" s="3">
         <v>1200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1000</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2748,8 +3070,10 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2786,8 +3110,14 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2824,8 +3154,14 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2862,8 +3198,14 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2900,46 +3242,58 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-6600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-6300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-3300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-3300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-1600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-1500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-400</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2976,8 +3330,14 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3014,8 +3374,14 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3052,46 +3418,58 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>500</v>
+      </c>
+      <c r="F76" s="3">
         <v>2800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>2700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>4900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-400</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3128,51 +3506,63 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3180,37 +3570,43 @@
         <v>-1600</v>
       </c>
       <c r="E81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G81" s="3">
         <v>-1500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-100</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3225,16 +3621,18 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
@@ -3251,11 +3649,11 @@
       <c r="J83" s="3">
         <v>0</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
+      <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
@@ -3263,8 +3661,14 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3301,8 +3705,14 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3339,8 +3749,14 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3377,8 +3793,14 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3415,8 +3837,14 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3453,37 +3881,43 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F89" s="3">
         <v>-900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-500</v>
       </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
+      <c r="L89" s="3">
+        <v>0</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
@@ -3491,8 +3925,14 @@
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3507,8 +3947,10 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3518,17 +3960,17 @@
       <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
+      <c r="F91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-100</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -3539,14 +3981,20 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3583,8 +4031,14 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3621,37 +4075,43 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-500</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
         <v>0</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
@@ -3659,8 +4119,14 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3675,8 +4141,10 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3701,11 +4169,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -3713,8 +4181,14 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3751,8 +4225,14 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3789,8 +4269,14 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3827,37 +4313,43 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>3200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>3200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>600</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
+      <c r="L100" s="3">
+        <v>0</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
@@ -3865,8 +4357,14 @@
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3876,11 +4374,11 @@
       <c r="E101" s="3">
         <v>0</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
@@ -3897,48 +4395,60 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-1200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>2300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>2300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>200</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
+      <c r="L102" s="3">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BREA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BREA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="92">
   <si>
     <t>BREA</t>
   </si>
@@ -656,99 +656,106 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>700</v>
+      </c>
+      <c r="E8" s="3">
+        <v>700</v>
+      </c>
+      <c r="F8" s="3">
         <v>900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>600</v>
       </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
       <c r="J8" s="3">
         <v>0</v>
       </c>
@@ -756,30 +763,36 @@
         <v>0</v>
       </c>
       <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
         <v>100</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3">
         <v>100</v>
@@ -788,10 +801,10 @@
         <v>100</v>
       </c>
       <c r="H9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
@@ -802,11 +815,11 @@
       <c r="L9" s="3">
         <v>0</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
+      <c r="M9" s="3">
+        <v>0</v>
+      </c>
+      <c r="N9" s="3">
+        <v>0</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
@@ -814,29 +827,35 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>700</v>
+      </c>
+      <c r="F10" s="3">
         <v>800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>500</v>
       </c>
-      <c r="H10" s="3">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3">
-        <v>0</v>
-      </c>
       <c r="J10" s="3">
         <v>0</v>
       </c>
@@ -844,22 +863,28 @@
         <v>0</v>
       </c>
       <c r="L10" s="3">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3">
         <v>100</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -876,8 +901,10 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -920,8 +947,14 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,8 +997,14 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -987,20 +1026,20 @@
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1008,23 +1047,29 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>100</v>
+      </c>
+      <c r="F15" s="3">
         <v>200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>200</v>
       </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
       <c r="H15" s="3">
         <v>0</v>
       </c>
@@ -1040,11 +1085,11 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>3</v>
@@ -1052,8 +1097,14 @@
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1067,87 +1118,95 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F17" s="3">
         <v>2600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>2700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>100</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-2200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-2100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-600</v>
       </c>
-      <c r="L18" s="3">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
+      <c r="N18" s="3">
+        <v>0</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
@@ -1155,8 +1214,14 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1173,29 +1238,31 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-400</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
@@ -1205,11 +1272,11 @@
       <c r="L20" s="3">
         <v>0</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
@@ -1217,43 +1284,49 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-1500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-1800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-1800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-600</v>
       </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
+      <c r="N21" s="3">
+        <v>0</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
@@ -1261,8 +1334,14 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1293,55 +1372,61 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-600</v>
       </c>
-      <c r="L23" s="3">
-        <v>0</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
+      <c r="N23" s="3">
+        <v>0</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
@@ -1349,22 +1434,28 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H24" s="3">
         <v>0</v>
@@ -1381,11 +1472,11 @@
       <c r="L24" s="3">
         <v>0</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
@@ -1393,8 +1484,14 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1437,96 +1534,114 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-100</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-1600</v>
+        <v>-800</v>
       </c>
       <c r="E27" s="3">
-        <v>-1600</v>
+        <v>-800</v>
       </c>
       <c r="F27" s="3">
         <v>-1600</v>
       </c>
       <c r="G27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I27" s="3">
         <v>-1500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-100</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1569,8 +1684,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1613,8 +1734,14 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1657,8 +1784,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1701,29 +1834,35 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>400</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
@@ -1733,11 +1872,11 @@
       <c r="L32" s="3">
         <v>0</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
@@ -1745,52 +1884,64 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-1600</v>
+        <v>-800</v>
       </c>
       <c r="E33" s="3">
-        <v>-1600</v>
+        <v>-800</v>
       </c>
       <c r="F33" s="3">
         <v>-1600</v>
       </c>
       <c r="G33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I33" s="3">
         <v>-1500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-100</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1833,101 +1984,119 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-1600</v>
+        <v>-800</v>
       </c>
       <c r="E35" s="3">
-        <v>-1600</v>
+        <v>-800</v>
       </c>
       <c r="F35" s="3">
         <v>-1600</v>
       </c>
       <c r="G35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I35" s="3">
         <v>-1500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-100</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1944,8 +2113,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1962,43 +2133,45 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F41" s="3">
         <v>500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>2400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>5000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>5000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>300</v>
       </c>
-      <c r="L41" s="3">
-        <v>0</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
+      <c r="N41" s="3">
+        <v>0</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
@@ -2006,16 +2179,22 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -2050,52 +2229,64 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F43" s="3">
         <v>800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>100</v>
       </c>
-      <c r="J43" s="3">
-        <v>0</v>
-      </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3">
         <v>100</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2105,11 +2296,11 @@
       <c r="E44" s="3">
         <v>0</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
+      <c r="F44" s="3">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3">
+        <v>0</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
@@ -2126,11 +2317,11 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
@@ -2138,8 +2329,14 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2161,18 +2358,18 @@
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2182,184 +2379,214 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F46" s="3">
         <v>1300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>3300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>3100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>5200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>5200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>200</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F47" s="3">
         <v>100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>100</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
-      </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1200</v>
+        <v>1900</v>
       </c>
       <c r="E48" s="3">
-        <v>1300</v>
+        <v>2100</v>
       </c>
       <c r="F48" s="3">
         <v>1200</v>
       </c>
       <c r="G48" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H48" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I48" s="3">
         <v>1100</v>
       </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
       <c r="J48" s="3">
+        <v>0</v>
+      </c>
+      <c r="K48" s="3">
+        <v>0</v>
+      </c>
+      <c r="L48" s="3">
         <v>300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>400</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F49" s="3">
         <v>4100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>4100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>4500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>4300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>900</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
+      <c r="M49" s="3">
+        <v>0</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2402,8 +2629,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2446,8 +2679,14 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2478,11 +2717,11 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
-      <c r="N52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O52" s="3">
         <v>0</v>
@@ -2490,8 +2729,14 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2534,52 +2779,64 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>11300</v>
+      </c>
+      <c r="F54" s="3">
         <v>6800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>6800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>9400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>9000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>6300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>6300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>600</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2596,8 +2853,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2614,60 +2873,68 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F57" s="3">
         <v>3000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>3100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>3900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>3700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E58" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F58" s="3">
         <v>300</v>
@@ -2676,25 +2943,25 @@
         <v>300</v>
       </c>
       <c r="H58" s="3">
+        <v>300</v>
+      </c>
+      <c r="I58" s="3">
+        <v>300</v>
+      </c>
+      <c r="J58" s="3">
         <v>200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>200</v>
-      </c>
-      <c r="J58" s="3">
-        <v>100</v>
-      </c>
-      <c r="K58" s="3">
-        <v>100</v>
       </c>
       <c r="L58" s="3">
         <v>100</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
+      <c r="M58" s="3">
+        <v>100</v>
+      </c>
+      <c r="N58" s="3">
+        <v>100</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
@@ -2702,8 +2969,14 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2714,16 +2987,16 @@
         <v>300</v>
       </c>
       <c r="F59" s="3">
+        <v>300</v>
+      </c>
+      <c r="G59" s="3">
+        <v>300</v>
+      </c>
+      <c r="H59" s="3">
         <v>600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>600</v>
-      </c>
-      <c r="H59" s="3">
-        <v>300</v>
-      </c>
-      <c r="I59" s="3">
-        <v>300</v>
       </c>
       <c r="J59" s="3">
         <v>300</v>
@@ -2732,101 +3005,113 @@
         <v>300</v>
       </c>
       <c r="L59" s="3">
+        <v>300</v>
+      </c>
+      <c r="M59" s="3">
+        <v>300</v>
+      </c>
+      <c r="N59" s="3">
         <v>500</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F60" s="3">
         <v>3900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>5000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>4800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>700</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="E61" s="3">
         <v>800</v>
       </c>
       <c r="F61" s="3">
+        <v>800</v>
+      </c>
+      <c r="G61" s="3">
+        <v>800</v>
+      </c>
+      <c r="H61" s="3">
         <v>900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>900</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L61" s="3">
         <v>300</v>
       </c>
       <c r="M61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="O61" s="3">
         <v>0</v>
@@ -2834,8 +3119,14 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2843,43 +3134,49 @@
         <v>1400</v>
       </c>
       <c r="E62" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F62" s="3">
         <v>1400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H62" s="3">
         <v>200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>400</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2922,8 +3219,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2966,8 +3269,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3010,52 +3319,64 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>6100</v>
+        <v>6500</v>
       </c>
       <c r="E66" s="3">
-        <v>6100</v>
+        <v>7000</v>
       </c>
       <c r="F66" s="3">
         <v>6100</v>
       </c>
       <c r="G66" s="3">
+        <v>6100</v>
+      </c>
+      <c r="H66" s="3">
+        <v>6100</v>
+      </c>
+      <c r="I66" s="3">
         <v>5900</v>
-      </c>
-      <c r="H66" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I66" s="3">
-        <v>1300</v>
       </c>
       <c r="J66" s="3">
         <v>1300</v>
       </c>
       <c r="K66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="M66" s="3">
         <v>1200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1000</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3072,8 +3393,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3116,8 +3439,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3160,8 +3489,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3204,8 +3539,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3248,52 +3589,64 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-9500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-9600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-6600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-6300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-3300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-3300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-1600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-1500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-400</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3336,8 +3689,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3380,8 +3739,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3424,52 +3789,64 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F76" s="3">
         <v>500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>2700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>5000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>4900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-400</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3512,101 +3889,119 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-1600</v>
+        <v>-800</v>
       </c>
       <c r="E81" s="3">
-        <v>-1600</v>
+        <v>-800</v>
       </c>
       <c r="F81" s="3">
         <v>-1600</v>
       </c>
       <c r="G81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I81" s="3">
         <v>-1500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-100</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3623,23 +4018,25 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
         <v>200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>200</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
       <c r="H83" s="3">
         <v>0</v>
       </c>
@@ -3655,11 +4052,11 @@
       <c r="L83" s="3">
         <v>0</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
@@ -3667,8 +4064,14 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3711,8 +4114,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3755,8 +4164,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3799,8 +4214,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3843,8 +4264,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3887,43 +4314,49 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-500</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
+      <c r="N89" s="3">
+        <v>0</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
@@ -3931,8 +4364,14 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3949,16 +4388,18 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F91" s="3">
         <v>-100</v>
@@ -3973,10 +4414,10 @@
         <v>-100</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -3987,14 +4428,20 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4037,8 +4484,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4081,43 +4534,49 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-500</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
@@ -4125,8 +4584,14 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4143,8 +4608,10 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4175,11 +4642,11 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -4187,8 +4654,14 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4231,8 +4704,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4275,8 +4754,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4319,43 +4804,49 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>3200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>3200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>600</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
+      <c r="N100" s="3">
+        <v>0</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
@@ -4363,8 +4854,14 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4380,11 +4877,11 @@
       <c r="G101" s="3">
         <v>0</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
@@ -4401,54 +4898,66 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>600</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-1000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>2300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>2300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>200</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
+      <c r="N102" s="3">
+        <v>0</v>
       </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BREA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BREA_QTR_FIN.xlsx
@@ -789,10 +789,10 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9" s="3">
         <v>100</v>
@@ -842,7 +842,7 @@
         <v>600</v>
       </c>
       <c r="E10" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="F10" s="3">
         <v>800</v>
@@ -1071,10 +1071,10 @@
         <v>200</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -1138,10 +1138,10 @@
         <v>2600</v>
       </c>
       <c r="H17" s="3">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="I17" s="3">
-        <v>2700</v>
+        <v>2600</v>
       </c>
       <c r="J17" s="3">
         <v>900</v>
@@ -1188,10 +1188,10 @@
         <v>-1700</v>
       </c>
       <c r="H18" s="3">
-        <v>-2200</v>
+        <v>-2100</v>
       </c>
       <c r="I18" s="3">
-        <v>-2100</v>
+        <v>-2000</v>
       </c>
       <c r="J18" s="3">
         <v>-800</v>
@@ -1246,7 +1246,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="E20" s="3">
         <v>-300</v>
@@ -1258,10 +1258,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="I20" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -1308,10 +1308,10 @@
         <v>-1500</v>
       </c>
       <c r="H21" s="3">
-        <v>-1800</v>
+        <v>-1700</v>
       </c>
       <c r="I21" s="3">
-        <v>-1800</v>
+        <v>-1600</v>
       </c>
       <c r="J21" s="3">
         <v>-800</v>
@@ -1846,7 +1846,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E32" s="3">
         <v>300</v>
@@ -1858,10 +1858,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I32" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -2191,10 +2191,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -2881,10 +2881,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E57" s="3">
         <v>3600</v>
-      </c>
-      <c r="E57" s="3">
-        <v>3800</v>
       </c>
       <c r="F57" s="3">
         <v>3000</v>
